--- a/schedule/Schedule.xlsx
+++ b/schedule/Schedule.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://canisius0-my.sharepoint.com/personal/mrowczy1_canisius_edu/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://canisius0-my.sharepoint.com/personal/mrowczy1_canisius_edu/Documents/Desktop/Fall 2026/common-syllabus-info/schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{726FD1CB-AD59-4E2E-B6E7-EF16CE1324B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{238E869C-E56E-4203-82B4-11E68F56C64E}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{726FD1CB-AD59-4E2E-B6E7-EF16CE1324B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDD6EDB9-6444-4CFF-8D1A-D44F0E84968E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{15434C29-7350-476F-88D5-74CAB56F0563}"/>
   </bookViews>
@@ -71,9 +71,6 @@
     <t>12:55PM</t>
   </si>
   <si>
-    <t>1PM</t>
-  </si>
-  <si>
     <t>1:55PM</t>
   </si>
   <si>
@@ -135,6 +132,9 @@
   </si>
   <si>
     <t>9:00AM</t>
+  </si>
+  <si>
+    <t>1:00PM</t>
   </si>
 </sst>
 </file>
@@ -293,6 +293,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -326,15 +347,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -352,18 +364,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -380,6 +380,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -733,15 +737,15 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24" t="s">
-        <v>22</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -749,156 +753,157 @@
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="6" t="s">
-        <v>27</v>
+      <c r="B3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="14"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="7"/>
+        <v>11</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="7"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="14"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="15"/>
+        <v>12</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="19" t="s">
+      <c r="D9" s="26"/>
+      <c r="E9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="15"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="15"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="15"/>
+        <v>28</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="15"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="15"/>
+        <v>13</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="15"/>
+        <v>15</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="16"/>
+        <v>16</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E9:E13"/>
     <mergeCell ref="F7:F15"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="E2:E4"/>
@@ -915,7 +920,6 @@
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D7:D10"/>
-    <mergeCell ref="E9:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="175" fitToWidth="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
